--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-process-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-process-hard.xlsx
@@ -460,10 +460,10 @@
         <v>Race condition hoặc lỗi dưới mạng yếu rất khó tái hiện trên môi trường dev local vốn có mạng rất nhanh. QA không được đóng bug nhạy cảm này. Cần cung cấp các công cụ giả lập (Network Throttling trong DevTools) và log chi tiết để chứng minh lỗi có tồn tại thực tế.</v>
       </c>
       <c r="F2" t="str">
+        <v>Đồng ý đóng bug theo yêu cầu của dev vì nếu dev không tái hiện được thì lỗi không tồn tại thực tế — đóng bug thụ động</v>
+      </c>
+      <c r="G2" t="str">
         <v>Giữ nguyên bug ở trạng thái Open, cung cấp thêm thông tin log mạng chi tiết (Fiddler/Charles proxy logs, console error, latency simulated), mô tả chính xác cách giả lập mạng yếu để hỗ trợ dev định vị race condition — kiên trì cung cấp bằng chứng kỹ thuật</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Đồng ý đóng bug theo yêu cầu của dev vì nếu dev không tái hiện được thì lỗi không tồn tại thực tế — đóng bug thụ động</v>
       </c>
       <c r="H2" t="str">
         <v>Tự ý nhảy vào sửa code của hệ thống để sửa lỗi này giúp lập trình viên — lấn sân lập trình viên</v>
@@ -472,7 +472,7 @@
         <v>Gửi email khiếu nại trực tiếp lên ban giám đốc để kỷ luật lập trình viên đó vì thái độ làm việc kém — khiếu nại nhân sự</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Defect Leakage Rate đo lường tỷ lệ bug lọt lưới lên môi trường thực tế (production). Tỷ lệ này cao chứng tỏ quy trình kiểm thử của team QA chưa tốt, bỏ sót nhiều kịch bản biên hoặc môi trường test không đồng bộ với production.</v>
       </c>
       <c r="F3" t="str">
+        <v>$\text{Defect Leakage Rate} = (\text{Số bug bị Dev Reject} / \text{Tổng số bug đã báo cáo}) \cdot 100\%$; phản ánh độ chính xác khi báo cáo lỗi của QA — tỷ lệ bug bị reject</v>
+      </c>
+      <c r="G3" t="str">
         <v>$\text{Defect Leakage Rate} = (\text{Bugs tìm thấy ở Production} / (\text{Bugs tìm thấy ở Test} + \text{Bugs tìm thấy ở Production})) \cdot 100\%$; phản ánh hiệu quả bao phủ của bộ test case — tỷ lệ rò rỉ lỗi lên production</v>
       </c>
-      <c r="G3" t="str">
-        <v>$\text{Defect Leakage Rate} = (\text{Số bug bị Dev Reject} / \text{Tổng số bug đã báo cáo}) \cdot 100\%$; phản ánh độ chính xác khi báo cáo lỗi của QA — tỷ lệ bug bị reject</v>
-      </c>
       <c r="H3" t="str">
+        <v>$\text{Defect Leakage Rate} = (\text{Số test case chạy fail} / \text{Tổng số test case đã chạy}) \cdot 100\%$; phản ánh mức độ nghiêm trọng của phần mềm — tỷ lệ test case fail</v>
+      </c>
+      <c r="I3" t="str">
         <v>$\text{Defect Leakage Rate} = (\text{Số dòng code bị lỗi} / \text{Tổng số dòng code đã viết}) \cdot 100\%$; phản ánh chất lượng code của lập trình viên — mật độ lỗi code</v>
       </c>
-      <c r="I3" t="str">
-        <v>$\text{Defect Leakage Rate} = (\text{Số test case chạy fail} / \text{Tổng số test case đã chạy}) \cdot 100\%$; phản ánh mức độ nghiêm trọng của phần mềm — tỷ lệ test case fail</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         <v>Chất trọng tài nằm ở PO/BA. Vì họ là người nắm rõ kỳ vọng của người dùng và yêu cầu nghiệp vụ của sản phẩm. Nếu tài liệu SRS/User Story chưa rõ ràng, PO/BA sẽ đưa ra quyết định làm rõ (clarification).</v>
       </c>
       <c r="F5" t="str">
-        <v>BA hoặc Product Owner (PO) là người sở hữu yêu cầu nghiệp vụ sẽ đứng ra phân xử và đưa ra quyết định cuối cùng; nếu là bug thì dev phải sửa, nếu là tính năng mới thì PO sẽ đưa vào backlog — PO/BA phân xử dựa trên nghiệp vụ</v>
+        <v>Developer có quyền tối cao quyết định đóng bug ngay lập tức mà không cần sự đồng ý của bất kỳ ai — quyền lực thuộc về developer</v>
       </c>
       <c r="G5" t="str">
         <v>Hai bên tự thương lượng bằng cách bỏ phiếu bình chọn trong group chat, bên nào có nhiều người ủng hộ hơn sẽ thắng — bỏ phiếu bình chọn</v>
       </c>
       <c r="H5" t="str">
-        <v>Developer có quyền tối cao quyết định đóng bug ngay lập tức mà không cần sự đồng ý của bất kỳ ai — quyền lực thuộc về developer</v>
+        <v>BA hoặc Product Owner (PO) là người sở hữu yêu cầu nghiệp vụ sẽ đứng ra phân xử và đưa ra quyết định cuối cùng; nếu là bug thì dev phải sửa, nếu là tính năng mới thì PO sẽ đưa vào backlog — PO/BA phân xử dựa trên nghiệp vụ</v>
       </c>
       <c r="I5" t="str">
         <v>Project Manager đứng ra ép buộc QA phải đóng bug ngay lập tức để báo cáo tiến độ đẹp cho khách hàng — PM lạm quyền ép đóng bug</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>DoD là hợp đồng chất lượng của Scrum Team để đảm bảo phần tăng trưởng sản phẩm (Increment) thực sự sẵn sàng phát hành. AC là hợp đồng nghiệp vụ giữa PO và team để đảm bảo tính năng chạy đúng logic nghiệp vụ cụ thể của story đó.</v>
       </c>
       <c r="F6" t="str">
-        <v>DoD áp dụng chung cho mọi User Story trong Sprint (như: đã code, đã peer-review, đã test, không còn bug block, đã deploy); AC là điều kiện nghiệm thu riêng biệt cho các tính năng nghiệp vụ của từng story đó — tiêu chuẩn chất lượng chung vs điều kiện nghiệm thu riêng biệt</v>
+        <v>DoD chỉ áp dụng cho mã nguồn Backend; còn AC chỉ áp dụng cho giao diện người dùng Frontend — phân loại theo layer công nghệ</v>
       </c>
       <c r="G6" t="str">
         <v>DoD do khách hàng phê duyệt; còn AC do lập trình viên tự kiểm thử và xác nhận hoàn thành — phân biệt chủ thể phê duyệt</v>
       </c>
       <c r="H6" t="str">
-        <v>DoD chỉ áp dụng cho mã nguồn Backend; còn AC chỉ áp dụng cho giao diện người dùng Frontend — phân loại theo layer công nghệ</v>
+        <v>DoD luôn được thay đổi tự do hàng ngày; còn AC không bao giờ được phép chỉnh sửa sau khi đã chốt — tính ổn định chỉ số</v>
       </c>
       <c r="I6" t="str">
-        <v>DoD luôn được thay đổi tự do hàng ngày; còn AC không bao giờ được phép chỉnh sửa sau khi đã chốt — tính ổn định chỉ số</v>
+        <v>DoD áp dụng chung cho mọi User Story trong Sprint (như: đã code, đã peer-review, đã test, không còn bug block, đã deploy); AC là điều kiện nghiệm thu riêng biệt cho các tính năng nghiệp vụ của từng story đó — tiêu chuẩn chất lượng chung vs điều kiện nghiệm thu riêng biệt</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Tích hợp bên thứ ba (như cổng thanh toán, hệ thống eKYC) luôn là rủi ro lớn nhất cho môi trường test (Sandboxes của đối tác thường bị sập hoặc giới hạn dữ liệu). Sử dụng Mock Server giúp QA hoàn toàn chủ động giả lập các kịch bản thành công và đặc biệt là các kịch bản lỗi biên của đối tác để test hệ thống của mình.</v>
       </c>
       <c r="F7" t="str">
+        <v>Rủi ro: Máy chủ của bệnh viện bị mất điện; Giải pháp: Yêu cầu bệnh viện mua thêm 10 chiếc máy phát điện dự phòng — can thiệp hạ tầng vật lý đối tác</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Rủi ro: Khách hàng không biết cách sử dụng ứng dụng di động; Giải pháp: QA tự đi viết toàn bộ tài liệu hướng dẫn sử dụng thay BA — đùn đẩy công việc của BA</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Rủi ro: Lập trình viên viết code sai cú pháp; Giải pháp: Yêu cầu lập trình viên phải đổi sang sử dụng máy tính chạy hệ điều hành MacOS — giải pháp phần cứng không liên quan</v>
+      </c>
+      <c r="I7" t="str">
         <v>Rủi ro: Môi trường test của bên thứ ba không ổn định hoặc không có sẵn dữ liệu test thực tế; Giải pháp: Yêu cầu team dev xây dựng hệ thống giả lập phản hồi (Mock Server/Stubs) để giả lập hành vi của các bên thứ ba — quản lý rủi ro môi trường liên kết</v>
       </c>
-      <c r="G7" t="str">
-        <v>Rủi ro: Lập trình viên viết code sai cú pháp; Giải pháp: Yêu cầu lập trình viên phải đổi sang sử dụng máy tính chạy hệ điều hành MacOS — giải pháp phần cứng không liên quan</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Rủi ro: Khách hàng không biết cách sử dụng ứng dụng di động; Giải pháp: QA tự đi viết toàn bộ tài liệu hướng dẫn sử dụng thay BA — đùn đẩy công việc của BA</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Rủi ro: Máy chủ của bệnh viện bị mất điện; Giải pháp: Yêu cầu bệnh viện mua thêm 10 chiếc máy phát điện dự phòng — can thiệp hạ tầng vật lý đối tác</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Defect Rejection Rate cao gây lãng phí tài nguyên của dự án (dev mất công kiểm tra rồi reject, QA mất công log). Nó phản ánh QA đang hấp tấp log bug mà chưa đọc kỹ tài liệu đặc tả, hoặc do tài liệu quá mơ hồ khiến các bên hiểu lệch pha nhau.</v>
       </c>
       <c r="F8" t="str">
+        <v>Tỷ lệ giữa số dòng code bị xóa bỏ chia cho tổng số dòng code đã viết; tỷ lệ cao cảnh báo code chất lượng kém — chất lượng mã nguồn</v>
+      </c>
+      <c r="G8" t="str">
         <v>Tỷ lệ giữa số bug bị dev reject (do hiểu sai spec, trùng lặp, hoặc không phải lỗi) chia cho tổng số bug đã báo cáo; tỷ lệ cao cảnh báo QA đang không nắm vững nghiệp vụ (SRS/AC) hoặc viết bug report mơ hồ — chất lượng báo cáo lỗi và hiểu nghiệp vụ của QA</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Tỷ lệ giữa số bug được sửa thành công chia cho tổng số bug đang mở; tỷ lệ cao cảnh báo dev đang làm việc quá tải — năng suất sửa bug của dev</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Tỷ lệ giữa số dòng code bị xóa bỏ chia cho tổng số dòng code đã viết; tỷ lệ cao cảnh báo code chất lượng kém — chất lượng mã nguồn</v>
       </c>
       <c r="I8" t="str">
         <v>Tỷ lệ giữa số test case bị viết sai cú pháp chia cho tổng số test case đã chạy; tỷ lệ cao cảnh báo năng lực viết test của QA kém — năng lực viết test case</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Hệ thống ERP lớn có hàng nghìn test cases. Chạy tay hàng tuần là không thể. Tự động hóa bộ test lõi (Regression Suite) giúp chạy nhanh qua đêm. Kết hợp Impact Analysis từ code change giúp QA khoanh vùng (scope) các khu vực có nguy cơ bị ảnh hưởng (side effects) để test tay bổ sung.</v>
       </c>
       <c r="F9" t="str">
+        <v>Yêu cầu toàn bộ các lập trình viên tự chạy test hồi quy trên máy của mình trước khi release — đùn đẩy trách nhiệm</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Bỏ qua hoàn toàn việc kiểm thử hồi quy, chỉ kiểm tra các tính năng mới viết thêm trong tuần đó — bỏ qua test hồi quy rủi ro cao</v>
+      </c>
+      <c r="H9" t="str">
         <v>Xây dựng bộ test case hồi quy cốt lõi (Regression Suite), tự động hóa các kịch bản test ổn định này bằng script test (Automation), và áp dụng phân tích tác động (Impact Analysis) để chỉ chạy thêm test case thủ công ở các vùng code bị ảnh hưởng trực tiếp bởi thay đổi — kết hợp Automation và phân tích tác động</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>Chạy lại toàn bộ 100% các test case thủ công có sẵn trong file Excel một cách tuần tự từ đầu đến cuối hàng tuần — chạy test thủ công toàn diện nặng nề</v>
       </c>
-      <c r="H9" t="str">
-        <v>Bỏ qua hoàn toàn việc kiểm thử hồi quy, chỉ kiểm tra các tính năng mới viết thêm trong tuần đó — bỏ qua test hồi quy rủi ro cao</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Yêu cầu toàn bộ các lập trình viên tự chạy test hồi quy trên máy của mình trước khi release — đùn đẩy trách nhiệm</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Lỗi phát hiện ở giai đoạn phân tích thiết kế chỉ tốn vài phút để sửa trong file Word. Lỗi phát hiện ở giai đoạn UAT/Production có thể tốn hàng nghìn USD và hàng tuần để sửa. Shift-Left Testing giúp phát hiện và ngăn chặn lỗi (Prevent defect) ngay từ trong trứng nước.</v>
       </c>
       <c r="F10" t="str">
+        <v>Bỏ qua hoàn toàn khâu viết tài liệu Test Plan để tập trung vào chạy code kiểm thử tự động ngay từ ngày đầu tiên — bỏ qua lập kế hoạch</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Yêu cầu lập trình viên phải viết code từ phải sang trái để dễ dàng phát hiện lỗi cú pháp hơn — viết ngược code</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Dịch chuyển toàn bộ bàn làm việc của các thành viên QA sang phía bên trái của văn phòng công ty — dịch chuyển vị trí vật lý</v>
+      </c>
+      <c r="I10" t="str">
         <v>Dịch chuyển các hoạt động kiểm thử về giai đoạn sớm nhất có thể của vòng đời phát triển (tham gia review yêu cầu, viết test case sớm, kiểm thử đơn vị, tĩnh), thay vì đợi có bản build hoàn chỉnh mới bắt đầu test — phát hiện lỗi sớm giảm chi phí</v>
       </c>
-      <c r="G10" t="str">
-        <v>Dịch chuyển toàn bộ bàn làm việc của các thành viên QA sang phía bên trái của văn phòng công ty — dịch chuyển vị trí vật lý</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Yêu cầu lập trình viên phải viết code từ phải sang trái để dễ dàng phát hiện lỗi cú pháp hơn — viết ngược code</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Bỏ qua hoàn toàn khâu viết tài liệu Test Plan để tập trung vào chạy code kiểm thử tự động ngay từ ngày đầu tiên — bỏ qua lập kế hoạch</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Test Summary Report cung cấp bức tranh toàn cảnh về chất lượng phần mềm hiện tại. QA Leader ký báo cáo này kèm theo khuyến nghị Go/No-Go làm căn cứ kỹ thuật để ban giám đốc hoặc khách hàng quyết định phát hành sản phẩm.</v>
       </c>
       <c r="F11" t="str">
+        <v>Quyết định tăng giá bán của sản phẩm phần mềm lên gấp đôi trên thị trường — quyết định định giá sản phẩm</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Quyết định lựa chọn công cụ kiểm thử tự động Selenium hay Playwright cho dự án tiếp theo — quyết định công nghệ test</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Quyết định sa thải lập trình viên nào đã làm phát sinh nhiều bug nhất trong dự án — quyết định sa thải nhân sự</v>
+      </c>
+      <c r="I11" t="str">
         <v>Quyết định phần mềm có đủ điều kiện chất lượng để Release go-live hay không dựa trên độ bao phủ test, số lượng bug còn tồn đọng và đánh giá rủi ro chất lượng — quyết định Go/No-Go release</v>
       </c>
-      <c r="G11" t="str">
-        <v>Quyết định sa thải lập trình viên nào đã làm phát sinh nhiều bug nhất trong dự án — quyết định sa thải nhân sự</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Quyết định tăng giá bán của sản phẩm phần mềm lên gấp đôi trên thị trường — quyết định định giá sản phẩm</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Quyết định lựa chọn công cụ kiểm thử tự động Selenium hay Playwright cho dự án tiếp theo — quyết định công nghệ test</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
